--- a/data/pareto_solutions.xlsx
+++ b/data/pareto_solutions.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="pareto_primary_rank" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="pareto_top20_primary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="pareto_weight_sensitivity" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="all_pareto_scores" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="method_summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pareto_primary_rank" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pareto_top20_primary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pareto_weight_sensitivity" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="all_pareto_scores" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="method_summary" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'pareto_primary_rank'!$A$1:$AD$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'pareto_top20_primary'!$A$1:$AD$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'pareto_weight_sensitivity'!$A$1:$I$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'all_pareto_scores'!$A$1:$AG$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'pareto_primary_rank'!$A$1:$AD$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'pareto_top20_primary'!$A$1:$AD$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'pareto_weight_sensitivity'!$A$1:$I$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'all_pareto_scores'!$A$1:$AG$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'method_summary'!$A$1:$B$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -620,7 +620,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>E0134</t>
+          <t>E122</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
@@ -632,7 +632,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         <v>3.9</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>0.5543092903158892</v>
+        <v>0.571908015718016</v>
       </c>
       <c r="J2" s="1" t="n">
         <v>1</v>
@@ -722,85 +722,77 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>E0275</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>MS-best-observed</t>
-        </is>
-      </c>
+          <t>E112</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr"/>
       <c r="C3" s="1" t="b">
         <v>1</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>276</v>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3390/su11154050</t>
-        </is>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="E3" s="1" t="inlineStr"/>
       <c r="F3" s="1" t="inlineStr">
         <is>
-          <t>Carbon_fiber</t>
+          <t>Mineral_fiber</t>
         </is>
       </c>
       <c r="G3" s="1" t="n">
-        <v>26.72</v>
+        <v>13.06</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>1.66</v>
+        <v>3.91</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>0.5355178670379396</v>
+        <v>0.5222795357362809</v>
       </c>
       <c r="J3" s="1" t="n">
         <v>2</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>60</v>
+        <v>91.8</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>42</v>
+        <v>49.6</v>
       </c>
       <c r="N3" s="1" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="O3" s="1" t="n">
-        <v>4.89</v>
+        <v>3.36</v>
       </c>
       <c r="P3" s="1" t="n">
-        <v>14.84</v>
+        <v>16.74975074775673</v>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>67.03</v>
+        <v>79.94</v>
       </c>
       <c r="R3" s="1" t="n">
-        <v>37.7</v>
+        <v>37</v>
       </c>
       <c r="S3" s="1" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T3" s="1" t="n">
-        <v>79.09999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="U3" s="1" t="inlineStr">
         <is>
-          <t>carbon</t>
+          <t>basalt</t>
         </is>
       </c>
       <c r="V3" s="1" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W3" s="1" t="n">
         <v>6</v>
       </c>
       <c r="X3" s="1" t="n">
-        <v>3500</v>
+        <v>2320</v>
       </c>
       <c r="Y3" s="1" t="inlineStr"/>
       <c r="Z3" s="1" t="n">
@@ -824,30 +816,38 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>E0277</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr"/>
+          <t>E263</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>MS-best-observed</t>
+        </is>
+      </c>
       <c r="C4" s="1" t="b">
         <v>1</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>278</v>
-      </c>
-      <c r="E4" s="1" t="inlineStr"/>
+        <v>264</v>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3390/su11154050</t>
+        </is>
+      </c>
       <c r="F4" s="1" t="inlineStr">
         <is>
           <t>Carbon_fiber</t>
         </is>
       </c>
       <c r="G4" s="1" t="n">
-        <v>24.95</v>
+        <v>26.72</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>0.5153669657534423</v>
+        <v>0.5159004471641312</v>
       </c>
       <c r="J4" s="1" t="n">
         <v>3</v>
@@ -862,16 +862,16 @@
         <v>42</v>
       </c>
       <c r="N4" s="1" t="n">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="O4" s="1" t="n">
-        <v>5.29</v>
+        <v>4.89</v>
       </c>
       <c r="P4" s="1" t="n">
-        <v>15.19</v>
+        <v>14.84</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>65.2</v>
+        <v>67.03</v>
       </c>
       <c r="R4" s="1" t="n">
         <v>37.7</v>
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="V4" s="1" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W4" s="1" t="n">
         <v>6</v>
@@ -918,7 +918,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>E0124</t>
+          <t>E265</t>
         </is>
       </c>
       <c r="B5" s="1" t="inlineStr"/>
@@ -926,69 +926,69 @@
         <v>1</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>125</v>
+        <v>266</v>
       </c>
       <c r="E5" s="1" t="inlineStr"/>
       <c r="F5" s="1" t="inlineStr">
         <is>
-          <t>Mineral_fiber</t>
+          <t>Carbon_fiber</t>
         </is>
       </c>
       <c r="G5" s="1" t="n">
-        <v>13.06</v>
+        <v>24.95</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>3.91</v>
+        <v>1.76</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>0.5031215387133503</v>
+        <v>0.4960598413938755</v>
       </c>
       <c r="J5" s="1" t="n">
         <v>4</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>91.8</v>
+        <v>60</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>49.6</v>
+        <v>42</v>
       </c>
       <c r="N5" s="1" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="O5" s="1" t="n">
-        <v>3.36</v>
+        <v>5.29</v>
       </c>
       <c r="P5" s="1" t="n">
-        <v>16.74975074775673</v>
+        <v>15.19</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>79.94</v>
+        <v>65.2</v>
       </c>
       <c r="R5" s="1" t="n">
-        <v>37</v>
+        <v>37.7</v>
       </c>
       <c r="S5" s="1" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="T5" s="1" t="n">
-        <v>76.5</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="U5" s="1" t="inlineStr">
         <is>
-          <t>basalt</t>
+          <t>carbon</t>
         </is>
       </c>
       <c r="V5" s="1" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W5" s="1" t="n">
         <v>6</v>
       </c>
       <c r="X5" s="1" t="n">
-        <v>2320</v>
+        <v>3500</v>
       </c>
       <c r="Y5" s="1" t="inlineStr"/>
       <c r="Z5" s="1" t="n">
@@ -1012,7 +1012,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>E0041</t>
+          <t>E239</t>
         </is>
       </c>
       <c r="B6" s="1" t="inlineStr">
@@ -1024,9 +1024,13 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>42</v>
-      </c>
-      <c r="E6" s="1" t="inlineStr"/>
+        <v>240</v>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3390/ma16020594</t>
+        </is>
+      </c>
       <c r="F6" s="1" t="inlineStr">
         <is>
           <t>Plastic_fiber</t>
@@ -1039,7 +1043,7 @@
         <v>3.94</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>0.464482132958237</v>
+        <v>0.4840995528322523</v>
       </c>
       <c r="J6" s="1" t="n">
         <v>5</v>
@@ -1054,7 +1058,7 @@
         <v>46.5</v>
       </c>
       <c r="N6" s="1" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="O6" s="1" t="n">
         <v>3.81</v>
@@ -1072,7 +1076,7 @@
       </c>
       <c r="U6" s="1" t="inlineStr">
         <is>
-          <t>Polyester Fiber</t>
+          <t>polyester</t>
         </is>
       </c>
       <c r="V6" s="1" t="n">
@@ -1110,7 +1114,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>E0251</t>
+          <t>E266</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr"/>
@@ -1118,81 +1122,81 @@
         <v>1</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="E7" s="1" t="inlineStr"/>
       <c r="F7" s="1" t="inlineStr">
         <is>
-          <t>Plastic_fiber</t>
+          <t>Carbon_fiber</t>
         </is>
       </c>
       <c r="G7" s="1" t="n">
-        <v>10.78</v>
+        <v>20.55</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>3.94</v>
+        <v>1.9</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>0.464482132958237</v>
+        <v>0.4017423428336878</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>85.90000000000001</v>
+        <v>60</v>
       </c>
       <c r="L7" s="1" t="n">
         <v>100</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>46.5</v>
+        <v>42</v>
       </c>
       <c r="N7" s="1" t="n">
-        <v>4</v>
+        <v>5.9</v>
       </c>
       <c r="O7" s="1" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="P7" s="1" t="inlineStr"/>
-      <c r="Q7" s="1" t="inlineStr"/>
+        <v>7.01</v>
+      </c>
+      <c r="P7" s="1" t="n">
+        <v>17.69</v>
+      </c>
+      <c r="Q7" s="1" t="n">
+        <v>60.35</v>
+      </c>
       <c r="R7" s="1" t="n">
-        <v>23</v>
+        <v>37.7</v>
       </c>
       <c r="S7" s="1" t="n">
-        <v>33.5</v>
+        <v>54</v>
       </c>
       <c r="T7" s="1" t="n">
-        <v>55.5</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="U7" s="1" t="inlineStr">
         <is>
-          <t>polyester</t>
+          <t>carbon</t>
         </is>
       </c>
       <c r="V7" s="1" t="n">
-        <v>0.23</v>
+        <v>0.8</v>
       </c>
       <c r="W7" s="1" t="n">
-        <v>0.02</v>
+        <v>6</v>
       </c>
       <c r="X7" s="1" t="n">
-        <v>591</v>
-      </c>
-      <c r="Y7" s="1" t="n">
-        <v>259</v>
-      </c>
+        <v>3500</v>
+      </c>
+      <c r="Y7" s="1" t="inlineStr"/>
       <c r="Z7" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AA7" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AB7" s="1" t="n">
-        <v>259</v>
-      </c>
+      <c r="AB7" s="1" t="inlineStr"/>
       <c r="AC7" s="1" t="inlineStr">
         <is>
-          <t>original_value_kept</t>
+          <t>unresolved_missing_no_same_type_MT_reference</t>
         </is>
       </c>
       <c r="AD7" s="1" t="inlineStr">
@@ -1204,7 +1208,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>E0278</t>
+          <t>E267</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr"/>
@@ -1212,7 +1216,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="E8" s="1" t="inlineStr"/>
       <c r="F8" s="1" t="inlineStr">
@@ -1221,13 +1225,13 @@
         </is>
       </c>
       <c r="G8" s="1" t="n">
-        <v>20.55</v>
+        <v>19.22</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>0.4167599746666855</v>
+        <v>0.3797721410096198</v>
       </c>
       <c r="J8" s="1" t="n">
         <v>7</v>
@@ -1242,16 +1246,16 @@
         <v>42</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>5.9</v>
+        <v>6.7</v>
       </c>
       <c r="O8" s="1" t="n">
-        <v>7.01</v>
+        <v>6.08</v>
       </c>
       <c r="P8" s="1" t="n">
-        <v>17.69</v>
+        <v>15.9</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>60.35</v>
+        <v>61.78</v>
       </c>
       <c r="R8" s="1" t="n">
         <v>37.7</v>
@@ -1298,7 +1302,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>E0279</t>
+          <t>E069</t>
         </is>
       </c>
       <c r="B9" s="1" t="inlineStr"/>
@@ -1306,81 +1310,83 @@
         <v>1</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>280</v>
+        <v>70</v>
       </c>
       <c r="E9" s="1" t="inlineStr"/>
       <c r="F9" s="1" t="inlineStr">
         <is>
-          <t>Carbon_fiber</t>
+          <t>No_fiber</t>
         </is>
       </c>
       <c r="G9" s="1" t="n">
-        <v>19.22</v>
+        <v>15.26</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>2.06</v>
+        <v>2.71</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>0.3915553426054078</v>
+        <v>0.3695888617124504</v>
       </c>
       <c r="J9" s="1" t="n">
         <v>8</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="L9" s="1" t="n">
         <v>100</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>6.7</v>
+        <v>4.3</v>
       </c>
       <c r="O9" s="1" t="n">
-        <v>6.08</v>
+        <v>3.9</v>
       </c>
       <c r="P9" s="1" t="n">
-        <v>15.9</v>
+        <v>12.1</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>61.78</v>
+        <v>67.77</v>
       </c>
       <c r="R9" s="1" t="n">
-        <v>37.7</v>
+        <v>26.6</v>
       </c>
       <c r="S9" s="1" t="n">
-        <v>54</v>
+        <v>37.9</v>
       </c>
       <c r="T9" s="1" t="n">
-        <v>79.09999999999999</v>
+        <v>58.3</v>
       </c>
       <c r="U9" s="1" t="inlineStr">
         <is>
-          <t>carbon</t>
+          <t>No_fiber</t>
         </is>
       </c>
       <c r="V9" s="1" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="W9" s="1" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="X9" s="1" t="n">
-        <v>3500</v>
-      </c>
-      <c r="Y9" s="1" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="Y9" s="1" t="n">
+        <v>0</v>
+      </c>
       <c r="Z9" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA9" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB9" s="1" t="inlineStr"/>
       <c r="AC9" s="1" t="inlineStr">
         <is>
-          <t>unresolved_missing_no_same_type_MT_reference</t>
+          <t>not_applicable_sample_no_fiber_set_to_0</t>
         </is>
       </c>
       <c r="AD9" s="1" t="inlineStr">
@@ -1392,7 +1398,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>E0081</t>
+          <t>E126</t>
         </is>
       </c>
       <c r="B10" s="1" t="inlineStr"/>
@@ -1400,83 +1406,75 @@
         <v>1</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="E10" s="1" t="inlineStr"/>
       <c r="F10" s="1" t="inlineStr">
         <is>
-          <t>No_fiber</t>
+          <t>Plastic_fiber</t>
         </is>
       </c>
       <c r="G10" s="1" t="n">
-        <v>15.26</v>
+        <v>15.56</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>2.71</v>
+        <v>2.33802816901408</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>0.3628018158538133</v>
+        <v>0.2987083640484909</v>
       </c>
       <c r="J10" s="1" t="n">
         <v>9</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>47</v>
-      </c>
-      <c r="L10" s="1" t="n">
-        <v>100</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="n">
-        <v>61</v>
+        <v>51.6</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>4.3</v>
+        <v>4.65</v>
       </c>
       <c r="O10" s="1" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="P10" s="1" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="Q10" s="1" t="n">
-        <v>67.77</v>
-      </c>
+        <v>4.41</v>
+      </c>
+      <c r="P10" s="1" t="inlineStr"/>
+      <c r="Q10" s="1" t="inlineStr"/>
       <c r="R10" s="1" t="n">
-        <v>26.6</v>
+        <v>39.06</v>
       </c>
       <c r="S10" s="1" t="n">
-        <v>37.9</v>
+        <v>48.63</v>
       </c>
       <c r="T10" s="1" t="n">
-        <v>58.3</v>
+        <v>76.27</v>
       </c>
       <c r="U10" s="1" t="inlineStr">
         <is>
-          <t>No_fiber</t>
+          <t>polyacrylonitrile</t>
         </is>
       </c>
       <c r="V10" s="1" t="n">
-        <v>0</v>
+        <v>0.075</v>
       </c>
       <c r="W10" s="1" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X10" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="1" t="n">
-        <v>0</v>
-      </c>
+        <v>780</v>
+      </c>
+      <c r="Y10" s="1" t="inlineStr"/>
       <c r="Z10" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA10" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB10" s="1" t="inlineStr"/>
       <c r="AC10" s="1" t="inlineStr">
         <is>
-          <t>not_applicable_sample_no_fiber_set_to_0</t>
+          <t>unresolved_missing_no_same_type_MT_reference</t>
         </is>
       </c>
       <c r="AD10" s="1" t="inlineStr">
@@ -1485,96 +1483,8 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>E0138</t>
-        </is>
-      </c>
-      <c r="B11" s="1" t="inlineStr"/>
-      <c r="C11" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>139</v>
-      </c>
-      <c r="E11" s="1" t="inlineStr"/>
-      <c r="F11" s="1" t="inlineStr">
-        <is>
-          <t>Plastic_fiber</t>
-        </is>
-      </c>
-      <c r="G11" s="1" t="n">
-        <v>15.56</v>
-      </c>
-      <c r="H11" s="1" t="n">
-        <v>2.33802816901408</v>
-      </c>
-      <c r="I11" s="1" t="n">
-        <v>0.2988053719886049</v>
-      </c>
-      <c r="J11" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="K11" s="1" t="n">
-        <v>57</v>
-      </c>
-      <c r="L11" s="1" t="inlineStr"/>
-      <c r="M11" s="1" t="n">
-        <v>51.6</v>
-      </c>
-      <c r="N11" s="1" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="O11" s="1" t="n">
-        <v>4.41</v>
-      </c>
-      <c r="P11" s="1" t="inlineStr"/>
-      <c r="Q11" s="1" t="inlineStr"/>
-      <c r="R11" s="1" t="n">
-        <v>39.06</v>
-      </c>
-      <c r="S11" s="1" t="n">
-        <v>48.63</v>
-      </c>
-      <c r="T11" s="1" t="n">
-        <v>76.27</v>
-      </c>
-      <c r="U11" s="1" t="inlineStr">
-        <is>
-          <t>polyacrylonitrile</t>
-        </is>
-      </c>
-      <c r="V11" s="1" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="W11" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="X11" s="1" t="n">
-        <v>780</v>
-      </c>
-      <c r="Y11" s="1" t="inlineStr"/>
-      <c r="Z11" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA11" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB11" s="1" t="inlineStr"/>
-      <c r="AC11" s="1" t="inlineStr">
-        <is>
-          <t>unresolved_missing_no_same_type_MT_reference</t>
-        </is>
-      </c>
-      <c r="AD11" s="1" t="inlineStr">
-        <is>
-          <t>observed_experimental</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AD11"/>
+  <autoFilter ref="A1:AD10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1585,7 +1495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1775,7 +1685,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>E0134</t>
+          <t>E122</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
@@ -1787,7 +1697,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
@@ -1806,7 +1716,7 @@
         <v>3.9</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>0.5543092903158892</v>
+        <v>0.571908015718016</v>
       </c>
       <c r="J2" s="1" t="n">
         <v>1</v>
@@ -1877,85 +1787,77 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>E0275</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>MS-best-observed</t>
-        </is>
-      </c>
+          <t>E112</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr"/>
       <c r="C3" s="1" t="b">
         <v>1</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>276</v>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3390/su11154050</t>
-        </is>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="E3" s="1" t="inlineStr"/>
       <c r="F3" s="1" t="inlineStr">
         <is>
-          <t>Carbon_fiber</t>
+          <t>Mineral_fiber</t>
         </is>
       </c>
       <c r="G3" s="1" t="n">
-        <v>26.72</v>
+        <v>13.06</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>1.66</v>
+        <v>3.91</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>0.5355178670379396</v>
+        <v>0.5222795357362809</v>
       </c>
       <c r="J3" s="1" t="n">
         <v>2</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>60</v>
+        <v>91.8</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>42</v>
+        <v>49.6</v>
       </c>
       <c r="N3" s="1" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="O3" s="1" t="n">
-        <v>4.89</v>
+        <v>3.36</v>
       </c>
       <c r="P3" s="1" t="n">
-        <v>14.84</v>
+        <v>16.74975074775673</v>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>67.03</v>
+        <v>79.94</v>
       </c>
       <c r="R3" s="1" t="n">
-        <v>37.7</v>
+        <v>37</v>
       </c>
       <c r="S3" s="1" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T3" s="1" t="n">
-        <v>79.09999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="U3" s="1" t="inlineStr">
         <is>
-          <t>carbon</t>
+          <t>basalt</t>
         </is>
       </c>
       <c r="V3" s="1" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W3" s="1" t="n">
         <v>6</v>
       </c>
       <c r="X3" s="1" t="n">
-        <v>3500</v>
+        <v>2320</v>
       </c>
       <c r="Y3" s="1" t="inlineStr"/>
       <c r="Z3" s="1" t="n">
@@ -1979,30 +1881,38 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>E0277</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr"/>
+          <t>E263</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>MS-best-observed</t>
+        </is>
+      </c>
       <c r="C4" s="1" t="b">
         <v>1</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>278</v>
-      </c>
-      <c r="E4" s="1" t="inlineStr"/>
+        <v>264</v>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3390/su11154050</t>
+        </is>
+      </c>
       <c r="F4" s="1" t="inlineStr">
         <is>
           <t>Carbon_fiber</t>
         </is>
       </c>
       <c r="G4" s="1" t="n">
-        <v>24.95</v>
+        <v>26.72</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>0.5153669657534423</v>
+        <v>0.5159004471641312</v>
       </c>
       <c r="J4" s="1" t="n">
         <v>3</v>
@@ -2017,16 +1927,16 @@
         <v>42</v>
       </c>
       <c r="N4" s="1" t="n">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="O4" s="1" t="n">
-        <v>5.29</v>
+        <v>4.89</v>
       </c>
       <c r="P4" s="1" t="n">
-        <v>15.19</v>
+        <v>14.84</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>65.2</v>
+        <v>67.03</v>
       </c>
       <c r="R4" s="1" t="n">
         <v>37.7</v>
@@ -2043,7 +1953,7 @@
         </is>
       </c>
       <c r="V4" s="1" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W4" s="1" t="n">
         <v>6</v>
@@ -2073,7 +1983,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>E0124</t>
+          <t>E265</t>
         </is>
       </c>
       <c r="B5" s="1" t="inlineStr"/>
@@ -2081,69 +1991,69 @@
         <v>1</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>125</v>
+        <v>266</v>
       </c>
       <c r="E5" s="1" t="inlineStr"/>
       <c r="F5" s="1" t="inlineStr">
         <is>
-          <t>Mineral_fiber</t>
+          <t>Carbon_fiber</t>
         </is>
       </c>
       <c r="G5" s="1" t="n">
-        <v>13.06</v>
+        <v>24.95</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>3.91</v>
+        <v>1.76</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>0.5031215387133503</v>
+        <v>0.4960598413938755</v>
       </c>
       <c r="J5" s="1" t="n">
         <v>4</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>91.8</v>
+        <v>60</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>49.6</v>
+        <v>42</v>
       </c>
       <c r="N5" s="1" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="O5" s="1" t="n">
-        <v>3.36</v>
+        <v>5.29</v>
       </c>
       <c r="P5" s="1" t="n">
-        <v>16.74975074775673</v>
+        <v>15.19</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>79.94</v>
+        <v>65.2</v>
       </c>
       <c r="R5" s="1" t="n">
-        <v>37</v>
+        <v>37.7</v>
       </c>
       <c r="S5" s="1" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="T5" s="1" t="n">
-        <v>76.5</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="U5" s="1" t="inlineStr">
         <is>
-          <t>basalt</t>
+          <t>carbon</t>
         </is>
       </c>
       <c r="V5" s="1" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W5" s="1" t="n">
         <v>6</v>
       </c>
       <c r="X5" s="1" t="n">
-        <v>2320</v>
+        <v>3500</v>
       </c>
       <c r="Y5" s="1" t="inlineStr"/>
       <c r="Z5" s="1" t="n">
@@ -2167,7 +2077,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>E0041</t>
+          <t>E239</t>
         </is>
       </c>
       <c r="B6" s="1" t="inlineStr">
@@ -2179,9 +2089,13 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>42</v>
-      </c>
-      <c r="E6" s="1" t="inlineStr"/>
+        <v>240</v>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3390/ma16020594</t>
+        </is>
+      </c>
       <c r="F6" s="1" t="inlineStr">
         <is>
           <t>Plastic_fiber</t>
@@ -2194,7 +2108,7 @@
         <v>3.94</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>0.464482132958237</v>
+        <v>0.4840995528322523</v>
       </c>
       <c r="J6" s="1" t="n">
         <v>5</v>
@@ -2209,7 +2123,7 @@
         <v>46.5</v>
       </c>
       <c r="N6" s="1" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="O6" s="1" t="n">
         <v>3.81</v>
@@ -2227,7 +2141,7 @@
       </c>
       <c r="U6" s="1" t="inlineStr">
         <is>
-          <t>Polyester Fiber</t>
+          <t>polyester</t>
         </is>
       </c>
       <c r="V6" s="1" t="n">
@@ -2265,7 +2179,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>E0251</t>
+          <t>E266</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr"/>
@@ -2273,81 +2187,81 @@
         <v>1</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="E7" s="1" t="inlineStr"/>
       <c r="F7" s="1" t="inlineStr">
         <is>
-          <t>Plastic_fiber</t>
+          <t>Carbon_fiber</t>
         </is>
       </c>
       <c r="G7" s="1" t="n">
-        <v>10.78</v>
+        <v>20.55</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>3.94</v>
+        <v>1.9</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>0.464482132958237</v>
+        <v>0.4017423428336878</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>85.90000000000001</v>
+        <v>60</v>
       </c>
       <c r="L7" s="1" t="n">
         <v>100</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>46.5</v>
+        <v>42</v>
       </c>
       <c r="N7" s="1" t="n">
-        <v>4</v>
+        <v>5.9</v>
       </c>
       <c r="O7" s="1" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="P7" s="1" t="inlineStr"/>
-      <c r="Q7" s="1" t="inlineStr"/>
+        <v>7.01</v>
+      </c>
+      <c r="P7" s="1" t="n">
+        <v>17.69</v>
+      </c>
+      <c r="Q7" s="1" t="n">
+        <v>60.35</v>
+      </c>
       <c r="R7" s="1" t="n">
-        <v>23</v>
+        <v>37.7</v>
       </c>
       <c r="S7" s="1" t="n">
-        <v>33.5</v>
+        <v>54</v>
       </c>
       <c r="T7" s="1" t="n">
-        <v>55.5</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="U7" s="1" t="inlineStr">
         <is>
-          <t>polyester</t>
+          <t>carbon</t>
         </is>
       </c>
       <c r="V7" s="1" t="n">
-        <v>0.23</v>
+        <v>0.8</v>
       </c>
       <c r="W7" s="1" t="n">
-        <v>0.02</v>
+        <v>6</v>
       </c>
       <c r="X7" s="1" t="n">
-        <v>591</v>
-      </c>
-      <c r="Y7" s="1" t="n">
-        <v>259</v>
-      </c>
+        <v>3500</v>
+      </c>
+      <c r="Y7" s="1" t="inlineStr"/>
       <c r="Z7" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AA7" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AB7" s="1" t="n">
-        <v>259</v>
-      </c>
+      <c r="AB7" s="1" t="inlineStr"/>
       <c r="AC7" s="1" t="inlineStr">
         <is>
-          <t>original_value_kept</t>
+          <t>unresolved_missing_no_same_type_MT_reference</t>
         </is>
       </c>
       <c r="AD7" s="1" t="inlineStr">
@@ -2359,7 +2273,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>E0278</t>
+          <t>E267</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr"/>
@@ -2367,7 +2281,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="E8" s="1" t="inlineStr"/>
       <c r="F8" s="1" t="inlineStr">
@@ -2376,13 +2290,13 @@
         </is>
       </c>
       <c r="G8" s="1" t="n">
-        <v>20.55</v>
+        <v>19.22</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>0.4167599746666855</v>
+        <v>0.3797721410096198</v>
       </c>
       <c r="J8" s="1" t="n">
         <v>7</v>
@@ -2397,16 +2311,16 @@
         <v>42</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>5.9</v>
+        <v>6.7</v>
       </c>
       <c r="O8" s="1" t="n">
-        <v>7.01</v>
+        <v>6.08</v>
       </c>
       <c r="P8" s="1" t="n">
-        <v>17.69</v>
+        <v>15.9</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>60.35</v>
+        <v>61.78</v>
       </c>
       <c r="R8" s="1" t="n">
         <v>37.7</v>
@@ -2453,7 +2367,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>E0279</t>
+          <t>E069</t>
         </is>
       </c>
       <c r="B9" s="1" t="inlineStr"/>
@@ -2461,81 +2375,83 @@
         <v>1</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>280</v>
+        <v>70</v>
       </c>
       <c r="E9" s="1" t="inlineStr"/>
       <c r="F9" s="1" t="inlineStr">
         <is>
-          <t>Carbon_fiber</t>
+          <t>No_fiber</t>
         </is>
       </c>
       <c r="G9" s="1" t="n">
-        <v>19.22</v>
+        <v>15.26</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>2.06</v>
+        <v>2.71</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>0.3915553426054078</v>
+        <v>0.3695888617124504</v>
       </c>
       <c r="J9" s="1" t="n">
         <v>8</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="L9" s="1" t="n">
         <v>100</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>6.7</v>
+        <v>4.3</v>
       </c>
       <c r="O9" s="1" t="n">
-        <v>6.08</v>
+        <v>3.9</v>
       </c>
       <c r="P9" s="1" t="n">
-        <v>15.9</v>
+        <v>12.1</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>61.78</v>
+        <v>67.77</v>
       </c>
       <c r="R9" s="1" t="n">
-        <v>37.7</v>
+        <v>26.6</v>
       </c>
       <c r="S9" s="1" t="n">
-        <v>54</v>
+        <v>37.9</v>
       </c>
       <c r="T9" s="1" t="n">
-        <v>79.09999999999999</v>
+        <v>58.3</v>
       </c>
       <c r="U9" s="1" t="inlineStr">
         <is>
-          <t>carbon</t>
+          <t>No_fiber</t>
         </is>
       </c>
       <c r="V9" s="1" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="W9" s="1" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="X9" s="1" t="n">
-        <v>3500</v>
-      </c>
-      <c r="Y9" s="1" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="Y9" s="1" t="n">
+        <v>0</v>
+      </c>
       <c r="Z9" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA9" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB9" s="1" t="inlineStr"/>
       <c r="AC9" s="1" t="inlineStr">
         <is>
-          <t>unresolved_missing_no_same_type_MT_reference</t>
+          <t>not_applicable_sample_no_fiber_set_to_0</t>
         </is>
       </c>
       <c r="AD9" s="1" t="inlineStr">
@@ -2547,7 +2463,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>E0081</t>
+          <t>E126</t>
         </is>
       </c>
       <c r="B10" s="1" t="inlineStr"/>
@@ -2555,83 +2471,75 @@
         <v>1</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="E10" s="1" t="inlineStr"/>
       <c r="F10" s="1" t="inlineStr">
         <is>
-          <t>No_fiber</t>
+          <t>Plastic_fiber</t>
         </is>
       </c>
       <c r="G10" s="1" t="n">
-        <v>15.26</v>
+        <v>15.56</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>2.71</v>
+        <v>2.33802816901408</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>0.3628018158538133</v>
+        <v>0.2987083640484909</v>
       </c>
       <c r="J10" s="1" t="n">
         <v>9</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>47</v>
-      </c>
-      <c r="L10" s="1" t="n">
-        <v>100</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="n">
-        <v>61</v>
+        <v>51.6</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>4.3</v>
+        <v>4.65</v>
       </c>
       <c r="O10" s="1" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="P10" s="1" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="Q10" s="1" t="n">
-        <v>67.77</v>
-      </c>
+        <v>4.41</v>
+      </c>
+      <c r="P10" s="1" t="inlineStr"/>
+      <c r="Q10" s="1" t="inlineStr"/>
       <c r="R10" s="1" t="n">
-        <v>26.6</v>
+        <v>39.06</v>
       </c>
       <c r="S10" s="1" t="n">
-        <v>37.9</v>
+        <v>48.63</v>
       </c>
       <c r="T10" s="1" t="n">
-        <v>58.3</v>
+        <v>76.27</v>
       </c>
       <c r="U10" s="1" t="inlineStr">
         <is>
-          <t>No_fiber</t>
+          <t>polyacrylonitrile</t>
         </is>
       </c>
       <c r="V10" s="1" t="n">
-        <v>0</v>
+        <v>0.075</v>
       </c>
       <c r="W10" s="1" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X10" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="1" t="n">
-        <v>0</v>
-      </c>
+        <v>780</v>
+      </c>
+      <c r="Y10" s="1" t="inlineStr"/>
       <c r="Z10" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA10" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB10" s="1" t="inlineStr"/>
       <c r="AC10" s="1" t="inlineStr">
         <is>
-          <t>not_applicable_sample_no_fiber_set_to_0</t>
+          <t>unresolved_missing_no_same_type_MT_reference</t>
         </is>
       </c>
       <c r="AD10" s="1" t="inlineStr">
@@ -2640,96 +2548,8 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>E0138</t>
-        </is>
-      </c>
-      <c r="B11" s="1" t="inlineStr"/>
-      <c r="C11" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>139</v>
-      </c>
-      <c r="E11" s="1" t="inlineStr"/>
-      <c r="F11" s="1" t="inlineStr">
-        <is>
-          <t>Plastic_fiber</t>
-        </is>
-      </c>
-      <c r="G11" s="1" t="n">
-        <v>15.56</v>
-      </c>
-      <c r="H11" s="1" t="n">
-        <v>2.33802816901408</v>
-      </c>
-      <c r="I11" s="1" t="n">
-        <v>0.2988053719886049</v>
-      </c>
-      <c r="J11" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="K11" s="1" t="n">
-        <v>57</v>
-      </c>
-      <c r="L11" s="1" t="inlineStr"/>
-      <c r="M11" s="1" t="n">
-        <v>51.6</v>
-      </c>
-      <c r="N11" s="1" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="O11" s="1" t="n">
-        <v>4.41</v>
-      </c>
-      <c r="P11" s="1" t="inlineStr"/>
-      <c r="Q11" s="1" t="inlineStr"/>
-      <c r="R11" s="1" t="n">
-        <v>39.06</v>
-      </c>
-      <c r="S11" s="1" t="n">
-        <v>48.63</v>
-      </c>
-      <c r="T11" s="1" t="n">
-        <v>76.27</v>
-      </c>
-      <c r="U11" s="1" t="inlineStr">
-        <is>
-          <t>polyacrylonitrile</t>
-        </is>
-      </c>
-      <c r="V11" s="1" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="W11" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="X11" s="1" t="n">
-        <v>780</v>
-      </c>
-      <c r="Y11" s="1" t="inlineStr"/>
-      <c r="Z11" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA11" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB11" s="1" t="inlineStr"/>
-      <c r="AC11" s="1" t="inlineStr">
-        <is>
-          <t>unresolved_missing_no_same_type_MT_reference</t>
-        </is>
-      </c>
-      <c r="AD11" s="1" t="inlineStr">
-        <is>
-          <t>observed_experimental</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AD11"/>
+  <autoFilter ref="A1:AD10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2740,7 +2560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2812,11 +2632,11 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>E0134</t>
+          <t>E122</t>
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
@@ -2835,7 +2655,7 @@
         <v>3.9</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>0.5543092903158892</v>
+        <v>0.571908015718016</v>
       </c>
     </row>
     <row r="3">
@@ -2849,30 +2669,26 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>E0275</t>
+          <t>E112</t>
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>276</v>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3390/su11154050</t>
-        </is>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="E3" s="1" t="inlineStr"/>
       <c r="F3" s="1" t="inlineStr">
         <is>
-          <t>Carbon_fiber</t>
+          <t>Mineral_fiber</t>
         </is>
       </c>
       <c r="G3" s="1" t="n">
-        <v>26.72</v>
+        <v>13.06</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>1.66</v>
+        <v>3.91</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>0.5355178670379396</v>
+        <v>0.5222795357362809</v>
       </c>
     </row>
     <row r="4">
@@ -2886,26 +2702,30 @@
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>E0277</t>
+          <t>E263</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>278</v>
-      </c>
-      <c r="E4" s="1" t="inlineStr"/>
+        <v>264</v>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3390/su11154050</t>
+        </is>
+      </c>
       <c r="F4" s="1" t="inlineStr">
         <is>
           <t>Carbon_fiber</t>
         </is>
       </c>
       <c r="G4" s="1" t="n">
-        <v>24.95</v>
+        <v>26.72</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>0.5153669657534423</v>
+        <v>0.5159004471641312</v>
       </c>
     </row>
     <row r="5">
@@ -2919,26 +2739,26 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>E0124</t>
+          <t>E265</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>125</v>
+        <v>266</v>
       </c>
       <c r="E5" s="1" t="inlineStr"/>
       <c r="F5" s="1" t="inlineStr">
         <is>
-          <t>Mineral_fiber</t>
+          <t>Carbon_fiber</t>
         </is>
       </c>
       <c r="G5" s="1" t="n">
-        <v>13.06</v>
+        <v>24.95</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>3.91</v>
+        <v>1.76</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>0.5031215387133503</v>
+        <v>0.4960598413938755</v>
       </c>
     </row>
     <row r="6">
@@ -2952,13 +2772,17 @@
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>E0041</t>
+          <t>E239</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>42</v>
-      </c>
-      <c r="E6" s="1" t="inlineStr"/>
+        <v>240</v>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3390/ma16020594</t>
+        </is>
+      </c>
       <c r="F6" s="1" t="inlineStr">
         <is>
           <t>Plastic_fiber</t>
@@ -2971,7 +2795,7 @@
         <v>3.94</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>0.464482132958237</v>
+        <v>0.4840995528322523</v>
       </c>
     </row>
     <row r="7">
@@ -2981,30 +2805,30 @@
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>E0251</t>
+          <t>E266</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="E7" s="1" t="inlineStr"/>
       <c r="F7" s="1" t="inlineStr">
         <is>
-          <t>Plastic_fiber</t>
+          <t>Carbon_fiber</t>
         </is>
       </c>
       <c r="G7" s="1" t="n">
-        <v>10.78</v>
+        <v>20.55</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>3.94</v>
+        <v>1.9</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>0.464482132958237</v>
+        <v>0.4017423428336878</v>
       </c>
     </row>
     <row r="8">
@@ -3018,11 +2842,11 @@
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>E0278</t>
+          <t>E267</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="E8" s="1" t="inlineStr"/>
       <c r="F8" s="1" t="inlineStr">
@@ -3031,13 +2855,13 @@
         </is>
       </c>
       <c r="G8" s="1" t="n">
-        <v>20.55</v>
+        <v>19.22</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>0.4167599746666855</v>
+        <v>0.3797721410096198</v>
       </c>
     </row>
     <row r="9">
@@ -3051,26 +2875,26 @@
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>E0279</t>
+          <t>E069</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>280</v>
+        <v>70</v>
       </c>
       <c r="E9" s="1" t="inlineStr"/>
       <c r="F9" s="1" t="inlineStr">
         <is>
-          <t>Carbon_fiber</t>
+          <t>No_fiber</t>
         </is>
       </c>
       <c r="G9" s="1" t="n">
-        <v>19.22</v>
+        <v>15.26</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>2.06</v>
+        <v>2.71</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>0.3915553426054078</v>
+        <v>0.3695888617124504</v>
       </c>
     </row>
     <row r="10">
@@ -3084,59 +2908,63 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>E0081</t>
+          <t>E126</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="E10" s="1" t="inlineStr"/>
       <c r="F10" s="1" t="inlineStr">
         <is>
-          <t>No_fiber</t>
+          <t>Plastic_fiber</t>
         </is>
       </c>
       <c r="G10" s="1" t="n">
-        <v>15.26</v>
+        <v>15.56</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>2.71</v>
+        <v>2.33802816901408</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>0.3628018158538133</v>
+        <v>0.2987083640484909</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>equal_weight</t>
+          <t>MS_preferred</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>E0138</t>
+          <t>E263</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>139</v>
-      </c>
-      <c r="E11" s="1" t="inlineStr"/>
+        <v>264</v>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3390/su11154050</t>
+        </is>
+      </c>
       <c r="F11" s="1" t="inlineStr">
         <is>
-          <t>Plastic_fiber</t>
+          <t>Carbon_fiber</t>
         </is>
       </c>
       <c r="G11" s="1" t="n">
-        <v>15.56</v>
+        <v>26.72</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>2.33802816901408</v>
+        <v>1.66</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>0.2988053719886049</v>
+        <v>0.6151679583489945</v>
       </c>
     </row>
     <row r="12">
@@ -3146,34 +2974,30 @@
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>E0275</t>
+          <t>E265</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>276</v>
-      </c>
-      <c r="E12" s="1" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3390/su11154050</t>
-        </is>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="E12" s="1" t="inlineStr"/>
       <c r="F12" s="1" t="inlineStr">
         <is>
           <t>Carbon_fiber</t>
         </is>
       </c>
       <c r="G12" s="1" t="n">
-        <v>26.72</v>
+        <v>24.95</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>0.633619514970891</v>
+        <v>0.5938172540899006</v>
       </c>
     </row>
     <row r="13">
@@ -3183,30 +3007,34 @@
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>E0277</t>
+          <t>E122</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>278</v>
-      </c>
-      <c r="E13" s="1" t="inlineStr"/>
+        <v>123</v>
+      </c>
+      <c r="E13" s="1" t="inlineStr">
+        <is>
+          <t>Chunli Wu 2020</t>
+        </is>
+      </c>
       <c r="F13" s="1" t="inlineStr">
         <is>
-          <t>Carbon_fiber</t>
+          <t>Mineral_fiber</t>
         </is>
       </c>
       <c r="G13" s="1" t="n">
-        <v>24.95</v>
+        <v>15.23</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>1.76</v>
+        <v>3.9</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>0.6119593997791989</v>
+        <v>0.4835664297843676</v>
       </c>
     </row>
     <row r="14">
@@ -3216,15 +3044,15 @@
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>E0278</t>
+          <t>E266</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="E14" s="1" t="inlineStr"/>
       <c r="F14" s="1" t="inlineStr">
@@ -3239,7 +3067,7 @@
         <v>1.9</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>0.4880347862490393</v>
+        <v>0.4752976350252251</v>
       </c>
     </row>
     <row r="15">
@@ -3249,34 +3077,30 @@
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>E0134</t>
+          <t>E267</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>135</v>
-      </c>
-      <c r="E15" s="1" t="inlineStr">
-        <is>
-          <t>Chunli Wu 2020</t>
-        </is>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="E15" s="1" t="inlineStr"/>
       <c r="F15" s="1" t="inlineStr">
         <is>
-          <t>Mineral_fiber</t>
+          <t>Carbon_fiber</t>
         </is>
       </c>
       <c r="G15" s="1" t="n">
-        <v>15.23</v>
+        <v>19.22</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>3.9</v>
+        <v>2.06</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>0.4675302989031586</v>
+        <v>0.4364604460114556</v>
       </c>
     </row>
     <row r="16">
@@ -3286,30 +3110,30 @@
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>E0279</t>
+          <t>E112</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>280</v>
+        <v>113</v>
       </c>
       <c r="E16" s="1" t="inlineStr"/>
       <c r="F16" s="1" t="inlineStr">
         <is>
-          <t>Carbon_fiber</t>
+          <t>Mineral_fiber</t>
         </is>
       </c>
       <c r="G16" s="1" t="n">
-        <v>19.22</v>
+        <v>13.06</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>2.06</v>
+        <v>3.91</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>0.4459278264956242</v>
+        <v>0.4250995020037299</v>
       </c>
     </row>
     <row r="17">
@@ -3319,30 +3143,34 @@
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>E0124</t>
+          <t>E239</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>125</v>
-      </c>
-      <c r="E17" s="1" t="inlineStr"/>
+        <v>240</v>
+      </c>
+      <c r="E17" s="1" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3390/ma16020594</t>
+        </is>
+      </c>
       <c r="F17" s="1" t="inlineStr">
         <is>
-          <t>Mineral_fiber</t>
+          <t>Plastic_fiber</t>
         </is>
       </c>
       <c r="G17" s="1" t="n">
-        <v>13.06</v>
+        <v>10.78</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>3.91</v>
+        <v>3.94</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>0.4070360287675856</v>
+        <v>0.3848320416474116</v>
       </c>
     </row>
     <row r="18">
@@ -3352,30 +3180,30 @@
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>E0041</t>
+          <t>E069</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="E18" s="1" t="inlineStr"/>
       <c r="F18" s="1" t="inlineStr">
         <is>
-          <t>Plastic_fiber</t>
+          <t>No_fiber</t>
         </is>
       </c>
       <c r="G18" s="1" t="n">
-        <v>10.78</v>
+        <v>15.26</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>3.94</v>
+        <v>2.71</v>
       </c>
       <c r="I18" s="1" t="n">
-        <v>0.3663804850253392</v>
+        <v>0.3363254972424943</v>
       </c>
     </row>
     <row r="19">
@@ -3385,15 +3213,15 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>E0251</t>
+          <t>E126</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>252</v>
+        <v>127</v>
       </c>
       <c r="E19" s="1" t="inlineStr"/>
       <c r="F19" s="1" t="inlineStr">
@@ -3402,79 +3230,83 @@
         </is>
       </c>
       <c r="G19" s="1" t="n">
-        <v>10.78</v>
+        <v>15.56</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>3.94</v>
+        <v>2.33802816901408</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>0.3663804850253392</v>
+        <v>0.2991743185811938</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>MS_preferred</t>
+          <t>ITS_preferred</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>E0081</t>
+          <t>E122</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>82</v>
-      </c>
-      <c r="E20" s="1" t="inlineStr"/>
+        <v>123</v>
+      </c>
+      <c r="E20" s="1" t="inlineStr">
+        <is>
+          <t>Chunli Wu 2020</t>
+        </is>
+      </c>
       <c r="F20" s="1" t="inlineStr">
         <is>
-          <t>No_fiber</t>
+          <t>Mineral_fiber</t>
         </is>
       </c>
       <c r="G20" s="1" t="n">
-        <v>15.26</v>
+        <v>15.23</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>2.71</v>
+        <v>3.9</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>0.3306692459002306</v>
+        <v>0.6617011545690442</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>MS_preferred</t>
+          <t>ITS_preferred</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>E0138</t>
+          <t>E112</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="E21" s="1" t="inlineStr"/>
       <c r="F21" s="1" t="inlineStr">
         <is>
-          <t>Plastic_fiber</t>
+          <t>Mineral_fiber</t>
         </is>
       </c>
       <c r="G21" s="1" t="n">
-        <v>15.56</v>
+        <v>13.06</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>2.33802816901408</v>
+        <v>3.91</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>0.2992507772815184</v>
+        <v>0.6196345028128787</v>
       </c>
     </row>
     <row r="22">
@@ -3484,34 +3316,34 @@
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t>E0134</t>
+          <t>E239</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>135</v>
+        <v>240</v>
       </c>
       <c r="E22" s="1" t="inlineStr">
         <is>
-          <t>Chunli Wu 2020</t>
+          <t>https://doi.org/10.3390/ma16020594</t>
         </is>
       </c>
       <c r="F22" s="1" t="inlineStr">
         <is>
-          <t>Mineral_fiber</t>
+          <t>Plastic_fiber</t>
         </is>
       </c>
       <c r="G22" s="1" t="n">
-        <v>15.23</v>
+        <v>10.78</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>3.9</v>
+        <v>3.94</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>0.6446508152024554</v>
+        <v>0.5846378647908284</v>
       </c>
     </row>
     <row r="23">
@@ -3521,30 +3353,34 @@
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>E0124</t>
+          <t>E263</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>125</v>
-      </c>
-      <c r="E23" s="1" t="inlineStr"/>
+        <v>264</v>
+      </c>
+      <c r="E23" s="1" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3390/su11154050</t>
+        </is>
+      </c>
       <c r="F23" s="1" t="inlineStr">
         <is>
-          <t>Mineral_fiber</t>
+          <t>Carbon_fiber</t>
         </is>
       </c>
       <c r="G23" s="1" t="n">
-        <v>13.06</v>
+        <v>26.72</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>3.91</v>
+        <v>1.66</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>0.6011446151244046</v>
+        <v>0.4153621352055318</v>
       </c>
     </row>
     <row r="24">
@@ -3554,30 +3390,30 @@
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C24" s="1" t="inlineStr">
         <is>
-          <t>E0041</t>
+          <t>E069</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="E24" s="1" t="inlineStr"/>
       <c r="F24" s="1" t="inlineStr">
         <is>
-          <t>Plastic_fiber</t>
+          <t>No_fiber</t>
         </is>
       </c>
       <c r="G24" s="1" t="n">
-        <v>10.78</v>
+        <v>15.26</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>3.94</v>
+        <v>2.71</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>0.5654114429310182</v>
+        <v>0.4032155203249566</v>
       </c>
     </row>
     <row r="25">
@@ -3587,30 +3423,30 @@
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>E0251</t>
+          <t>E265</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="E25" s="1" t="inlineStr"/>
       <c r="F25" s="1" t="inlineStr">
         <is>
-          <t>Plastic_fiber</t>
+          <t>Carbon_fiber</t>
         </is>
       </c>
       <c r="G25" s="1" t="n">
-        <v>10.78</v>
+        <v>24.95</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>3.94</v>
+        <v>1.76</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>0.5654114429310182</v>
+        <v>0.397550291284623</v>
       </c>
     </row>
     <row r="26">
@@ -3620,34 +3456,30 @@
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t>E0275</t>
+          <t>E266</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>276</v>
-      </c>
-      <c r="E26" s="1" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3390/su11154050</t>
-        </is>
-      </c>
+        <v>267</v>
+      </c>
+      <c r="E26" s="1" t="inlineStr"/>
       <c r="F26" s="1" t="inlineStr">
         <is>
           <t>Carbon_fiber</t>
         </is>
       </c>
       <c r="G26" s="1" t="n">
-        <v>26.72</v>
+        <v>20.55</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>1.66</v>
+        <v>1.9</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>0.4345885570651034</v>
+        <v>0.3236888424718649</v>
       </c>
     </row>
     <row r="27">
@@ -3657,15 +3489,15 @@
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>E0277</t>
+          <t>E267</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="E27" s="1" t="inlineStr"/>
       <c r="F27" s="1" t="inlineStr">
@@ -3674,13 +3506,13 @@
         </is>
       </c>
       <c r="G27" s="1" t="n">
-        <v>24.95</v>
+        <v>19.22</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>1.76</v>
+        <v>2.06</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>0.4163147532035721</v>
+        <v>0.3181101710724414</v>
       </c>
     </row>
     <row r="28">
@@ -3690,133 +3522,34 @@
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>E0081</t>
+          <t>E126</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="E28" s="1" t="inlineStr"/>
       <c r="F28" s="1" t="inlineStr">
         <is>
-          <t>No_fiber</t>
+          <t>Plastic_fiber</t>
         </is>
       </c>
       <c r="G28" s="1" t="n">
-        <v>15.26</v>
+        <v>15.56</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>2.71</v>
+        <v>2.33802816901408</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>0.3971103005199207</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>ITS_preferred</t>
-        </is>
-      </c>
-      <c r="B29" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>E0278</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="n">
-        <v>279</v>
-      </c>
-      <c r="E29" s="1" t="inlineStr"/>
-      <c r="F29" s="1" t="inlineStr">
-        <is>
-          <t>Carbon_fiber</t>
-        </is>
-      </c>
-      <c r="G29" s="1" t="n">
-        <v>20.55</v>
-      </c>
-      <c r="H29" s="1" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="I29" s="1" t="n">
-        <v>0.3386042517824212</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>ITS_preferred</t>
-        </is>
-      </c>
-      <c r="B30" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="C30" s="1" t="inlineStr">
-        <is>
-          <t>E0279</t>
-        </is>
-      </c>
-      <c r="D30" s="1" t="n">
-        <v>280</v>
-      </c>
-      <c r="E30" s="1" t="inlineStr"/>
-      <c r="F30" s="1" t="inlineStr">
-        <is>
-          <t>Carbon_fiber</t>
-        </is>
-      </c>
-      <c r="G30" s="1" t="n">
-        <v>19.22</v>
-      </c>
-      <c r="H30" s="1" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="I30" s="1" t="n">
-        <v>0.3298534458291759</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>ITS_preferred</t>
-        </is>
-      </c>
-      <c r="B31" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>E0138</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="n">
-        <v>139</v>
-      </c>
-      <c r="E31" s="1" t="inlineStr"/>
-      <c r="F31" s="1" t="inlineStr">
-        <is>
-          <t>Plastic_fiber</t>
-        </is>
-      </c>
-      <c r="G31" s="1" t="n">
-        <v>15.56</v>
-      </c>
-      <c r="H31" s="1" t="n">
-        <v>2.33802816901408</v>
-      </c>
-      <c r="I31" s="1" t="n">
-        <v>0.2983083010761932</v>
+        <v>0.2982186162613725</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I31"/>
+  <autoFilter ref="A1:I28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3827,7 +3560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG11"/>
+  <dimension ref="A1:AG10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4035,79 +3768,81 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>E0041</t>
+          <t>E069</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="C2" s="1" t="inlineStr"/>
       <c r="D2" s="1" t="n">
-        <v>85.90000000000001</v>
+        <v>47</v>
       </c>
       <c r="E2" s="1" t="n">
         <v>100</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>46.5</v>
+        <v>61</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="I2" s="1" t="inlineStr"/>
-      <c r="J2" s="1" t="inlineStr"/>
+        <v>3.9</v>
+      </c>
+      <c r="I2" s="1" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="J2" s="1" t="n">
+        <v>67.77</v>
+      </c>
       <c r="K2" s="1" t="n">
-        <v>23</v>
+        <v>26.6</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>33.5</v>
+        <v>37.9</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>55.5</v>
+        <v>58.3</v>
       </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
-          <t>Polyester Fiber</t>
+          <t>No_fiber</t>
         </is>
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>Plastic_fiber</t>
+          <t>No_fiber</t>
         </is>
       </c>
       <c r="P2" s="1" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R2" s="1" t="n">
-        <v>591</v>
+        <v>0</v>
       </c>
       <c r="S2" s="1" t="n">
-        <v>259</v>
+        <v>0</v>
       </c>
       <c r="T2" s="1" t="n">
-        <v>10.78</v>
+        <v>15.26</v>
       </c>
       <c r="U2" s="1" t="n">
-        <v>3.94</v>
+        <v>2.71</v>
       </c>
       <c r="V2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" s="1" t="n">
-        <v>259</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="X2" s="1" t="inlineStr"/>
       <c r="Y2" s="1" t="inlineStr">
         <is>
-          <t>original_value_kept</t>
+          <t>not_applicable_sample_no_fiber_set_to_0</t>
         </is>
       </c>
       <c r="Z2" s="1" t="inlineStr">
@@ -4119,102 +3854,100 @@
         <v>1</v>
       </c>
       <c r="AB2" s="1" t="n">
-        <v>0.464482132958237</v>
+        <v>0.3695888617124504</v>
       </c>
       <c r="AC2" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD2" s="1" t="n">
+        <v>0.3363254972424943</v>
+      </c>
+      <c r="AE2" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF2" s="1" t="n">
+        <v>0.4032155203249566</v>
+      </c>
+      <c r="AG2" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="AD2" s="1" t="n">
-        <v>0.3663804850253392</v>
-      </c>
-      <c r="AE2" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="AF2" s="1" t="n">
-        <v>0.5654114429310182</v>
-      </c>
-      <c r="AG2" s="1" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>E0081</t>
+          <t>E112</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="C3" s="1" t="inlineStr"/>
       <c r="D3" s="1" t="n">
-        <v>47</v>
+        <v>91.8</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>61</v>
+        <v>49.6</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>3.9</v>
+        <v>3.36</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>12.1</v>
+        <v>16.74975074775673</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>67.77</v>
+        <v>79.94</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>26.6</v>
+        <v>37</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>37.9</v>
+        <v>53</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>58.3</v>
+        <v>76.5</v>
       </c>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>No_fiber</t>
+          <t>basalt</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>No_fiber</t>
+          <t>Mineral_fiber</t>
         </is>
       </c>
       <c r="P3" s="1" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R3" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="1" t="n">
-        <v>0</v>
-      </c>
+        <v>2320</v>
+      </c>
+      <c r="S3" s="1" t="inlineStr"/>
       <c r="T3" s="1" t="n">
-        <v>15.26</v>
+        <v>13.06</v>
       </c>
       <c r="U3" s="1" t="n">
-        <v>2.71</v>
+        <v>3.91</v>
       </c>
       <c r="V3" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W3" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X3" s="1" t="inlineStr"/>
       <c r="Y3" s="1" t="inlineStr">
         <is>
-          <t>not_applicable_sample_no_fiber_set_to_0</t>
+          <t>unresolved_missing_no_same_type_MT_reference</t>
         </is>
       </c>
       <c r="Z3" s="1" t="inlineStr">
@@ -4226,63 +3959,67 @@
         <v>1</v>
       </c>
       <c r="AB3" s="1" t="n">
-        <v>0.3628018158538133</v>
+        <v>0.5222795357362809</v>
       </c>
       <c r="AC3" s="1" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AD3" s="1" t="n">
-        <v>0.3306692459002306</v>
+        <v>0.4250995020037299</v>
       </c>
       <c r="AE3" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AF3" s="1" t="n">
-        <v>0.3971103005199207</v>
+        <v>0.6196345028128787</v>
       </c>
       <c r="AG3" s="1" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>E0124</t>
+          <t>E122</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>125</v>
-      </c>
-      <c r="C4" s="1" t="inlineStr"/>
+        <v>123</v>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Chunli Wu 2020</t>
+        </is>
+      </c>
       <c r="D4" s="1" t="n">
-        <v>91.8</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>150</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>49.6</v>
+        <v>46.9</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>5.8</v>
+        <v>5.27</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>3.36</v>
+        <v>3.1</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>16.74975074775673</v>
+        <v>14.2</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>79.94</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>37</v>
+        <v>33.9</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>53</v>
+        <v>54.8</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>76.5</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="N4" s="1" t="inlineStr">
         <is>
@@ -4295,7 +4032,7 @@
         </is>
       </c>
       <c r="P4" s="1" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="Q4" s="1" t="n">
         <v>6</v>
@@ -4305,10 +4042,10 @@
       </c>
       <c r="S4" s="1" t="inlineStr"/>
       <c r="T4" s="1" t="n">
-        <v>13.06</v>
+        <v>15.23</v>
       </c>
       <c r="U4" s="1" t="n">
-        <v>3.91</v>
+        <v>3.9</v>
       </c>
       <c r="V4" s="1" t="n">
         <v>1</v>
@@ -4331,93 +4068,83 @@
         <v>1</v>
       </c>
       <c r="AB4" s="1" t="n">
-        <v>0.5031215387133503</v>
+        <v>0.571908015718016</v>
       </c>
       <c r="AC4" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AD4" s="1" t="n">
-        <v>0.4070360287675856</v>
+        <v>0.4835664297843676</v>
       </c>
       <c r="AE4" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AF4" s="1" t="n">
-        <v>0.6011446151244046</v>
+        <v>0.6617011545690442</v>
       </c>
       <c r="AG4" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>E0134</t>
+          <t>E126</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>135</v>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>Chunli Wu 2020</t>
-        </is>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="C5" s="1" t="inlineStr"/>
       <c r="D5" s="1" t="n">
-        <v>91.59999999999999</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>150</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="E5" s="1" t="inlineStr"/>
       <c r="F5" s="1" t="n">
-        <v>46.9</v>
+        <v>51.6</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>5.27</v>
+        <v>4.65</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="I5" s="1" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="J5" s="1" t="n">
-        <v>78.59999999999999</v>
-      </c>
+        <v>4.41</v>
+      </c>
+      <c r="I5" s="1" t="inlineStr"/>
+      <c r="J5" s="1" t="inlineStr"/>
       <c r="K5" s="1" t="n">
-        <v>33.9</v>
+        <v>39.06</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>54.8</v>
+        <v>48.63</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>80.90000000000001</v>
+        <v>76.27</v>
       </c>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>basalt</t>
+          <t>polyacrylonitrile</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>Mineral_fiber</t>
+          <t>Plastic_fiber</t>
         </is>
       </c>
       <c r="P5" s="1" t="n">
-        <v>0.2</v>
+        <v>0.075</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R5" s="1" t="n">
-        <v>2320</v>
+        <v>780</v>
       </c>
       <c r="S5" s="1" t="inlineStr"/>
       <c r="T5" s="1" t="n">
-        <v>15.23</v>
+        <v>15.56</v>
       </c>
       <c r="U5" s="1" t="n">
-        <v>3.9</v>
+        <v>2.33802816901408</v>
       </c>
       <c r="V5" s="1" t="n">
         <v>1</v>
@@ -4440,61 +4167,67 @@
         <v>1</v>
       </c>
       <c r="AB5" s="1" t="n">
-        <v>0.5543092903158892</v>
+        <v>0.2987083640484909</v>
       </c>
       <c r="AC5" s="1" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AD5" s="1" t="n">
-        <v>0.4675302989031586</v>
+        <v>0.2991743185811938</v>
       </c>
       <c r="AE5" s="1" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AF5" s="1" t="n">
-        <v>0.6446508152024554</v>
+        <v>0.2982186162613725</v>
       </c>
       <c r="AG5" s="1" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>E0138</t>
+          <t>E239</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>139</v>
-      </c>
-      <c r="C6" s="1" t="inlineStr"/>
+        <v>240</v>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3390/ma16020594</t>
+        </is>
+      </c>
       <c r="D6" s="1" t="n">
-        <v>57</v>
-      </c>
-      <c r="E6" s="1" t="inlineStr"/>
+        <v>85.90000000000001</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>100</v>
+      </c>
       <c r="F6" s="1" t="n">
-        <v>51.6</v>
+        <v>46.5</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>4.65</v>
+        <v>4</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>4.41</v>
+        <v>3.81</v>
       </c>
       <c r="I6" s="1" t="inlineStr"/>
       <c r="J6" s="1" t="inlineStr"/>
       <c r="K6" s="1" t="n">
-        <v>39.06</v>
+        <v>23</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>48.63</v>
+        <v>33.5</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>76.27</v>
+        <v>55.5</v>
       </c>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>polyacrylonitrile</t>
+          <t>polyester</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr">
@@ -4503,20 +4236,22 @@
         </is>
       </c>
       <c r="P6" s="1" t="n">
-        <v>0.075</v>
+        <v>0.23</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R6" s="1" t="n">
-        <v>780</v>
-      </c>
-      <c r="S6" s="1" t="inlineStr"/>
+        <v>591</v>
+      </c>
+      <c r="S6" s="1" t="n">
+        <v>259</v>
+      </c>
       <c r="T6" s="1" t="n">
-        <v>15.56</v>
+        <v>10.78</v>
       </c>
       <c r="U6" s="1" t="n">
-        <v>2.33802816901408</v>
+        <v>3.94</v>
       </c>
       <c r="V6" s="1" t="n">
         <v>1</v>
@@ -4524,10 +4259,12 @@
       <c r="W6" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="X6" s="1" t="inlineStr"/>
+      <c r="X6" s="1" t="n">
+        <v>259</v>
+      </c>
       <c r="Y6" s="1" t="inlineStr">
         <is>
-          <t>unresolved_missing_no_same_type_MT_reference</t>
+          <t>original_value_kept</t>
         </is>
       </c>
       <c r="Z6" s="1" t="inlineStr">
@@ -4539,143 +4276,143 @@
         <v>1</v>
       </c>
       <c r="AB6" s="1" t="n">
-        <v>0.2988053719886049</v>
+        <v>0.4840995528322523</v>
       </c>
       <c r="AC6" s="1" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AD6" s="1" t="n">
-        <v>0.2992507772815184</v>
+        <v>0.3848320416474116</v>
       </c>
       <c r="AE6" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF6" s="1" t="n">
-        <v>0.2983083010761932</v>
+        <v>0.5846378647908284</v>
       </c>
       <c r="AG6" s="1" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>E0251</t>
+          <t>E263</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>252</v>
-      </c>
-      <c r="C7" s="1" t="inlineStr"/>
+        <v>264</v>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3390/su11154050</t>
+        </is>
+      </c>
       <c r="D7" s="1" t="n">
-        <v>85.90000000000001</v>
+        <v>60</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>100</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>46.5</v>
+        <v>42</v>
       </c>
       <c r="G7" s="1" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>14.84</v>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>67.03</v>
+      </c>
+      <c r="K7" s="1" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="L7" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="N7" s="1" t="inlineStr">
+        <is>
+          <t>carbon</t>
+        </is>
+      </c>
+      <c r="O7" s="1" t="inlineStr">
+        <is>
+          <t>Carbon_fiber</t>
+        </is>
+      </c>
+      <c r="P7" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q7" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="R7" s="1" t="n">
+        <v>3500</v>
+      </c>
+      <c r="S7" s="1" t="inlineStr"/>
+      <c r="T7" s="1" t="n">
+        <v>26.72</v>
+      </c>
+      <c r="U7" s="1" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" s="1" t="inlineStr"/>
+      <c r="Y7" s="1" t="inlineStr">
+        <is>
+          <t>unresolved_missing_no_same_type_MT_reference</t>
+        </is>
+      </c>
+      <c r="Z7" s="1" t="inlineStr">
+        <is>
+          <t>observed_experimental</t>
+        </is>
+      </c>
+      <c r="AA7" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB7" s="1" t="n">
+        <v>0.5159004471641312</v>
+      </c>
+      <c r="AC7" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD7" s="1" t="n">
+        <v>0.6151679583489945</v>
+      </c>
+      <c r="AE7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF7" s="1" t="n">
+        <v>0.4153621352055318</v>
+      </c>
+      <c r="AG7" s="1" t="n">
         <v>4</v>
-      </c>
-      <c r="H7" s="1" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="I7" s="1" t="inlineStr"/>
-      <c r="J7" s="1" t="inlineStr"/>
-      <c r="K7" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="L7" s="1" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="M7" s="1" t="n">
-        <v>55.5</v>
-      </c>
-      <c r="N7" s="1" t="inlineStr">
-        <is>
-          <t>polyester</t>
-        </is>
-      </c>
-      <c r="O7" s="1" t="inlineStr">
-        <is>
-          <t>Plastic_fiber</t>
-        </is>
-      </c>
-      <c r="P7" s="1" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="Q7" s="1" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="R7" s="1" t="n">
-        <v>591</v>
-      </c>
-      <c r="S7" s="1" t="n">
-        <v>259</v>
-      </c>
-      <c r="T7" s="1" t="n">
-        <v>10.78</v>
-      </c>
-      <c r="U7" s="1" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="V7" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="W7" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="X7" s="1" t="n">
-        <v>259</v>
-      </c>
-      <c r="Y7" s="1" t="inlineStr">
-        <is>
-          <t>original_value_kept</t>
-        </is>
-      </c>
-      <c r="Z7" s="1" t="inlineStr">
-        <is>
-          <t>observed_experimental</t>
-        </is>
-      </c>
-      <c r="AA7" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB7" s="1" t="n">
-        <v>0.464482132958237</v>
-      </c>
-      <c r="AC7" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD7" s="1" t="n">
-        <v>0.3663804850253392</v>
-      </c>
-      <c r="AE7" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="AF7" s="1" t="n">
-        <v>0.5654114429310182</v>
-      </c>
-      <c r="AG7" s="1" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>E0275</t>
+          <t>E265</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>276</v>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3390/su11154050</t>
-        </is>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="C8" s="1" t="inlineStr"/>
       <c r="D8" s="1" t="n">
         <v>60</v>
       </c>
@@ -4686,16 +4423,16 @@
         <v>42</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>4.89</v>
+        <v>5.29</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>14.84</v>
+        <v>15.19</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>67.03</v>
+        <v>65.2</v>
       </c>
       <c r="K8" s="1" t="n">
         <v>37.7</v>
@@ -4717,7 +4454,7 @@
         </is>
       </c>
       <c r="P8" s="1" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="Q8" s="1" t="n">
         <v>6</v>
@@ -4727,10 +4464,10 @@
       </c>
       <c r="S8" s="1" t="inlineStr"/>
       <c r="T8" s="1" t="n">
-        <v>26.72</v>
+        <v>24.95</v>
       </c>
       <c r="U8" s="1" t="n">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="V8" s="1" t="n">
         <v>1</v>
@@ -4753,32 +4490,32 @@
         <v>1</v>
       </c>
       <c r="AB8" s="1" t="n">
-        <v>0.5355178670379396</v>
+        <v>0.4960598413938755</v>
       </c>
       <c r="AC8" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD8" s="1" t="n">
+        <v>0.5938172540899006</v>
+      </c>
+      <c r="AE8" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="AD8" s="1" t="n">
-        <v>0.633619514970891</v>
-      </c>
-      <c r="AE8" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="AF8" s="1" t="n">
-        <v>0.4345885570651034</v>
+        <v>0.397550291284623</v>
       </c>
       <c r="AG8" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>E0277</t>
+          <t>E266</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="C9" s="1" t="inlineStr"/>
       <c r="D9" s="1" t="n">
@@ -4791,16 +4528,16 @@
         <v>42</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>5.29</v>
+        <v>7.01</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>15.19</v>
+        <v>17.69</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>65.2</v>
+        <v>60.35</v>
       </c>
       <c r="K9" s="1" t="n">
         <v>37.7</v>
@@ -4822,7 +4559,7 @@
         </is>
       </c>
       <c r="P9" s="1" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="Q9" s="1" t="n">
         <v>6</v>
@@ -4832,10 +4569,10 @@
       </c>
       <c r="S9" s="1" t="inlineStr"/>
       <c r="T9" s="1" t="n">
-        <v>24.95</v>
+        <v>20.55</v>
       </c>
       <c r="U9" s="1" t="n">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="V9" s="1" t="n">
         <v>1</v>
@@ -4858,32 +4595,32 @@
         <v>1</v>
       </c>
       <c r="AB9" s="1" t="n">
-        <v>0.5153669657534423</v>
+        <v>0.4017423428336878</v>
       </c>
       <c r="AC9" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AD9" s="1" t="n">
-        <v>0.6119593997791989</v>
+        <v>0.4752976350252251</v>
       </c>
       <c r="AE9" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF9" s="1" t="n">
-        <v>0.4163147532035721</v>
+        <v>0.3236888424718649</v>
       </c>
       <c r="AG9" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>E0278</t>
+          <t>E267</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="C10" s="1" t="inlineStr"/>
       <c r="D10" s="1" t="n">
@@ -4896,16 +4633,16 @@
         <v>42</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>5.9</v>
+        <v>6.7</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>7.01</v>
+        <v>6.08</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>17.69</v>
+        <v>15.9</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>60.35</v>
+        <v>61.78</v>
       </c>
       <c r="K10" s="1" t="n">
         <v>37.7</v>
@@ -4937,10 +4674,10 @@
       </c>
       <c r="S10" s="1" t="inlineStr"/>
       <c r="T10" s="1" t="n">
-        <v>20.55</v>
+        <v>19.22</v>
       </c>
       <c r="U10" s="1" t="n">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="V10" s="1" t="n">
         <v>1</v>
@@ -4963,131 +4700,26 @@
         <v>1</v>
       </c>
       <c r="AB10" s="1" t="n">
-        <v>0.4167599746666855</v>
+        <v>0.3797721410096198</v>
       </c>
       <c r="AC10" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AD10" s="1" t="n">
-        <v>0.4880347862490393</v>
+        <v>0.4364604460114556</v>
       </c>
       <c r="AE10" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AF10" s="1" t="n">
-        <v>0.3386042517824212</v>
+        <v>0.3181101710724414</v>
       </c>
       <c r="AG10" s="1" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>E0279</t>
-        </is>
-      </c>
-      <c r="B11" s="1" t="n">
-        <v>280</v>
-      </c>
-      <c r="C11" s="1" t="inlineStr"/>
-      <c r="D11" s="1" t="n">
-        <v>60</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="F11" s="1" t="n">
-        <v>42</v>
-      </c>
-      <c r="G11" s="1" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="H11" s="1" t="n">
-        <v>6.08</v>
-      </c>
-      <c r="I11" s="1" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="J11" s="1" t="n">
-        <v>61.78</v>
-      </c>
-      <c r="K11" s="1" t="n">
-        <v>37.7</v>
-      </c>
-      <c r="L11" s="1" t="n">
-        <v>54</v>
-      </c>
-      <c r="M11" s="1" t="n">
-        <v>79.09999999999999</v>
-      </c>
-      <c r="N11" s="1" t="inlineStr">
-        <is>
-          <t>carbon</t>
-        </is>
-      </c>
-      <c r="O11" s="1" t="inlineStr">
-        <is>
-          <t>Carbon_fiber</t>
-        </is>
-      </c>
-      <c r="P11" s="1" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Q11" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="R11" s="1" t="n">
-        <v>3500</v>
-      </c>
-      <c r="S11" s="1" t="inlineStr"/>
-      <c r="T11" s="1" t="n">
-        <v>19.22</v>
-      </c>
-      <c r="U11" s="1" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="V11" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="W11" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="X11" s="1" t="inlineStr"/>
-      <c r="Y11" s="1" t="inlineStr">
-        <is>
-          <t>unresolved_missing_no_same_type_MT_reference</t>
-        </is>
-      </c>
-      <c r="Z11" s="1" t="inlineStr">
-        <is>
-          <t>observed_experimental</t>
-        </is>
-      </c>
-      <c r="AA11" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB11" s="1" t="n">
-        <v>0.3915553426054078</v>
-      </c>
-      <c r="AC11" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD11" s="1" t="n">
-        <v>0.4459278264956242</v>
-      </c>
-      <c r="AE11" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="AF11" s="1" t="n">
-        <v>0.3298534458291759</v>
-      </c>
-      <c r="AG11" s="1" t="n">
-        <v>9</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AG11"/>
+  <autoFilter ref="A1:AG10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5148,7 +4780,7 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>401</v>
+        <v>389</v>
       </c>
     </row>
     <row r="5">
@@ -5158,7 +4790,7 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
